--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2947-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2947-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{081A708B-A888-424D-9700-14CADE771CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D836187E-B6F4-428D-95AC-E1A2F3D5085C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{87636967-CB9E-4136-B397-EC5CB55FB3D1}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{F7DF011F-8ABB-452B-876C-CF5671397377}"/>
   </bookViews>
   <sheets>
     <sheet name="2947-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1561,18 +1561,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4D1773D-F316-45CC-992C-D9EC774A7FF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{924B784A-5309-4569-AC6F-D89BBFA8EDFD}">
   <dimension ref="A1:R23"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1600,7 +1600,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1630,7 +1630,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1726,7 +1726,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1806,7 +1806,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1862,7 +1862,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>2025</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="53" t="s">
         <v>27</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="54"/>
       <c r="B11" s="24" t="s">
         <v>32</v>
@@ -2050,7 +2050,7 @@
       <c r="Q11" s="58"/>
       <c r="R11" s="58"/>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="63">
         <v>2024</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="51">
         <v>2023</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>27</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="63">
         <v>2022</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>27</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>3.62</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="51">
         <v>2021</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="63">
         <v>2020</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51" t="s">
         <v>45</v>
       </c>
